--- a/IPAnalyzer/traffic.xlsx
+++ b/IPAnalyzer/traffic.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referrers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Popular Paths" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downloads" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Views" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Clones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Referrers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Popular Paths" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Downloads" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Stats" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="9" min="1" max="1"/>
@@ -489,62 +489,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="10">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Views</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Unique Visitors</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Views</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unique Visitors</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Total Views</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unique Visitors</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Total Views</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Unique Visitors</t>
         </is>
@@ -553,14 +553,14 @@
     <row r="2" ht="15" customHeight="1" s="10">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -590,23 +590,23 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="10">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
         <v>4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -634,14 +634,14 @@
     <row r="4" ht="15" customHeight="1" s="10">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
         <v>5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -658,14 +658,14 @@
     <row r="5" ht="15" customHeight="1" s="10">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -682,115 +682,115 @@
     <row r="6" ht="15" customHeight="1" s="10">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="10">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="10">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="10">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="10">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="10">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="10">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -799,7 +799,7 @@
     <row r="15" ht="15" customHeight="1" s="10">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -812,33 +812,33 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -851,13 +851,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B22" t="n">
         <v>7</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C22" t="n">
         <v>4</v>
       </c>
     </row>
@@ -874,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="9" min="1" max="1"/>
@@ -892,62 +931,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="10">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Clones</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Unique Cloners</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Clones</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unique Cloners</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Total Clones</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unique Cloners</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Total Clones</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Unique Cloners</t>
         </is>
@@ -956,14 +995,14 @@
     <row r="2" ht="15" customHeight="1" s="10">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -971,10 +1010,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -982,10 +1021,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="K2" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -993,23 +1032,23 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="O2" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="10">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1037,14 +1076,14 @@
     <row r="4" ht="15" customHeight="1" s="10">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1061,14 +1100,14 @@
     <row r="5" ht="15" customHeight="1" s="10">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1085,20 +1124,20 @@
     <row r="6" ht="15" customHeight="1" s="10">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1111,46 +1150,46 @@
     <row r="8" ht="15" customHeight="1" s="10">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="10">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="10">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1163,46 +1202,46 @@
     <row r="12" ht="15" customHeight="1" s="10">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="10">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="10">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="10">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1215,52 +1254,91 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B22" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1277,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="9" min="1" max="1"/>
@@ -1299,82 +1377,82 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="10">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date Collected</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
@@ -1383,35 +1461,35 @@
     <row r="2" ht="15" customHeight="1" s="10">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>yseto.net</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1424,10 +1502,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="N2" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -1440,82 +1518,82 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="S2" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="10">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>yseto.net</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="H3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>38</v>
+      </c>
+      <c r="N3" t="n">
         <v>12</v>
       </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>yseto.net</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>38</v>
+      </c>
+      <c r="S3" t="n">
         <v>12</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>21</v>
-      </c>
-      <c r="S3" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1524,10 +1602,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1540,10 +1618,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1556,10 +1634,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1572,28 +1650,28 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1615,7 +1693,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1627,7 +1705,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1649,19 +1727,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>github.com</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1676,10 +1754,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1690,14 +1768,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1708,14 +1786,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1726,14 +1804,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1757,25 +1835,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1793,36 +1871,90 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>yseto.net</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>yseto.net</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1839,7 +1971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:W66"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="9" min="1" max="1"/>
@@ -1865,102 +1997,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="10">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date Collected</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="W1" s="29" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
@@ -1969,7 +2101,7 @@
     <row r="2" ht="15" customHeight="1" s="10">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1983,10 +2115,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2004,10 +2136,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -2025,10 +2157,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -2046,16 +2178,16 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="W2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="10">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2069,7 +2201,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>6</v>
@@ -2090,10 +2222,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2111,10 +2243,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -2132,54 +2264,54 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="W3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="10">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.977</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.3.977</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>/releases/tag/v.3.974</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>/releases/tag/v.3.974</t>
-        </is>
-      </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2188,20 +2320,20 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="P4" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q4" t="n">
         <v>41</v>
       </c>
-      <c r="Q4" t="n">
-        <v>22</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>2026</t>
@@ -2209,128 +2341,128 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="V4" t="n">
+        <v>51</v>
+      </c>
+      <c r="W4" t="n">
         <v>41</v>
-      </c>
-      <c r="W4" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="10">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.3.974</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.977</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.3.977</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>/releases/tag/v.3.973</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>/releases/tag/v.3.973</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>/seto77/IPAnalyzer</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>31</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>/seto77/IPAnalyzer</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
       <c r="V5" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="W5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="10">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/issues</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2348,10 +2480,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2369,10 +2501,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -2390,33 +2522,33 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.961</t>
+          <t>/releases/tag/v.3.976</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2425,19 +2557,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.961</t>
+          <t>/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2446,19 +2578,19 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.977</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>/releases/tag/v.3.977</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -2467,121 +2599,121 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.977</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>/releases/tag/v.3.977</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="10">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>/seto77/IPAnalyzer/issues</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>/issues</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.3.976</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>/releases/tag/v.3.975</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>/releases/tag/v.3.975</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>/seto77/ipanalyzer/pulls</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>/pulls</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>/seto77/ipanalyzer/pulls</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>/pulls</t>
-        </is>
-      </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="10">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.976</t>
+          <t>/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2597,19 +2729,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.976</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2627,10 +2759,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2648,16 +2780,16 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2683,19 +2815,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2704,19 +2836,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.975</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2725,39 +2857,39 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.975</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -2769,19 +2901,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer/pulls</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2790,19 +2922,19 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commits</t>
+          <t>/seto77/ipanalyzer/pulls</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>/commits</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -2811,63 +2943,63 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commits</t>
+          <t>/seto77/ipanalyzer/pulls</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>/commits</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.974</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.974</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2876,19 +3008,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>/blob/master/LICENSE.md</t>
+          <t>/releases/tag/v.3.976</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2897,25 +3029,25 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>/blob/master/LICENSE.md</t>
+          <t>/releases/tag/v.3.976</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2929,10 +3061,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2941,19 +3073,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K13" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2962,16 +3094,16 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/seto77/IPAnalyzer/pulls</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -2983,16 +3115,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/seto77/IPAnalyzer/pulls</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W13" t="n">
         <v>2</v>
@@ -3001,7 +3133,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3027,19 +3159,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/IPAnalyzer/releases</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>38</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3048,19 +3180,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
+          <t>/seto77/IPAnalyzer/commits</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.976</t>
+          <t>/commits</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3069,42 +3201,42 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
+          <t>/seto77/IPAnalyzer/commits</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.976</t>
+          <t>/commits</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3113,19 +3245,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3134,19 +3266,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>/blob/master/LICENSE.md</t>
         </is>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -3155,42 +3287,42 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>/blob/master/LICENSE.md</t>
         </is>
       </c>
       <c r="V15" t="n">
         <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
+          <t>/seto77/IPAnalyzer/issues</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.974</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3199,42 +3331,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>24</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3243,12 +3417,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/issues</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -3261,24 +3435,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.974</t>
+          <t>/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3287,12 +3461,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>/seto77/ipanalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer/issues</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -3305,24 +3479,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.976</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.3.976</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3331,42 +3505,42 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commits</t>
+          <t>/seto77/ipanalyzer/pulls</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>/commits</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/IPAnalyzer/pulls</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3375,12 +3549,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
+          <t>/seto77/IPAnalyzer/commits</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.961</t>
+          <t>/commits</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -3393,24 +3567,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3419,12 +3593,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.975</t>
+          <t>/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3442,40 +3616,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.3.975</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-W15</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>/blob/master/LICENSE.md</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3486,20 +3660,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/IPAnalyzer/releases</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026-W15</t>
@@ -3507,12 +3681,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/blob/master/LICENSE.md</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -3530,20 +3704,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3553,19 +3748,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer</t>
+          <t>/seto77/IPAnalyzer/releases</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -3576,16 +3771,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -3599,19 +3794,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer</t>
+          <t>/seto77/IPAnalyzer/releases</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -3622,19 +3817,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -3645,19 +3840,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/issues</t>
+          <t>/seto77/IPAnalyzer/releases</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -3668,19 +3863,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>/seto77/ipanalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -3691,19 +3886,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -3714,19 +3909,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commits</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/commits</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3737,19 +3932,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/issues</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -3760,19 +3955,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.961</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -3783,19 +3978,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.975</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -3806,19 +4001,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>/seto77/ipanalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -3829,19 +4024,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -3852,12 +4047,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commits</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/commits</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -3898,12 +4093,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
+          <t>/seto77/ipanalyzer/pulls</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.961</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -3921,12 +4116,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.975</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -3944,12 +4139,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>/seto77/ipanalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer/commits</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>/commits</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -3967,12 +4162,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer/issues</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -3990,12 +4185,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commits</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/commits</t>
+          <t>/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -4013,12 +4208,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/issues</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -4036,12 +4231,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
+          <t>/seto77/ipanalyzer/pulls</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.961</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -4059,12 +4254,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.975</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4082,12 +4277,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>/seto77/ipanalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer/commits</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>/commits</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -4100,99 +4295,99 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/IPAnalyzer/issues</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.974</t>
+          <t>/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer</t>
+          <t>/seto77/ipanalyzer/pulls</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4215,17 +4410,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
+          <t>/seto77/IPAnalyzer/commits</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/blob/master/LICENSE.md</t>
+          <t>/commits</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -4238,17 +4433,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/seto77/IPAnalyzer/issues</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -4261,17 +4456,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/issues</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases/tag/v.3.961</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -4284,17 +4479,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>/seto77/ipanalyzer/pulls</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/pulls</t>
+          <t>/releases/tag/v.3.975</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -4307,132 +4502,132 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+          <t>/seto77/ipanalyzer/pulls</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.973</t>
+          <t>/pulls</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.3.973</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
+          <t>/seto77/IPAnalyzer/releases</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/releases/tag/v.3.974</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer</t>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/releases/tag/v.3.974</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/actions</t>
+          <t>/seto77/IPAnalyzer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/actions</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
+          <t>/seto77/IPAnalyzer/actions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/blob/master/LICENSE.md</t>
+          <t>/actions</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -4445,17 +4640,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+          <t>/blob/master/LICENSE.md</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -4468,17 +4663,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>/seto77/IPAnalyzer/issues</t>
+          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -4491,23 +4686,253 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/issues</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>/issues</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>/seto77/ipanalyzer/pulls</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>/pulls</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.973</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.3.973</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>9</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/releases</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>/releases</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>6</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/releases/tag/v.3.974</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.3.974</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/actions</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>/actions</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/blob/master/LICENSE.md</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>/blob/master/LICENSE.md</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>/commit/ae73adbc89acbabdb78c7a591074542a065fcc56</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>/seto77/IPAnalyzer/issues</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>/issues</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>/seto77/ipanalyzer/pulls</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>/pulls</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="n">
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4539,22 +4964,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Release Tag</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Release Date</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Download Count</t>
         </is>
@@ -4577,7 +5002,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -6161,13 +6586,13 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D82" s="30" t="n">
-        <v>4309</v>
+      <c r="D82" t="n">
+        <v>4316</v>
       </c>
     </row>
   </sheetData>
@@ -6181,7 +6606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="9" min="1" max="1"/>
@@ -6207,102 +6632,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="10">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Open Issues</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Watchers</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Open Issues</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Watchers</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Open Issues</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Watchers</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Open Issues</t>
         </is>
       </c>
-      <c r="W1" s="29" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Watchers</t>
         </is>
@@ -6311,7 +6736,7 @@
     <row r="2" ht="15" customHeight="1" s="10">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -6324,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6341,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6358,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -6375,13 +6800,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -6394,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -6417,7 +6842,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6430,13 +6855,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6449,6 +6874,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>3</v>
       </c>
     </row>
